--- a/data/trans_camb/P2C_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,69</t>
+          <t>0,4; 5,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,98</t>
+          <t>-0,3; 3,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 21,35</t>
+          <t>6,67; 21,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,74</t>
+          <t>-1,57; 5,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,65</t>
+          <t>-1,61; 4,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 18,06</t>
+          <t>4,63; 19,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,42</t>
+          <t>0,43; 4,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,17</t>
+          <t>-0,27; 3,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,03</t>
+          <t>7,13; 17,99</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,35; —</t>
+          <t>-58,89; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>305,42; —</t>
+          <t>348,54; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 761,92</t>
+          <t>-67,42; 692,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 760,69</t>
+          <t>-63,53; 609,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,09; 2171,05</t>
+          <t>106,62; 2411,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 680,96</t>
+          <t>9,24; 913,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 579,2</t>
+          <t>-24,77; 519,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>339,74; 3089,26</t>
+          <t>345,61; 3188,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,74</t>
+          <t>-6,01; 0,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 1,26</t>
+          <t>-5,42; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 19,22</t>
+          <t>2,66; 17,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,1</t>
+          <t>-1,53; 2,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,26</t>
+          <t>-1,49; 3,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 22,65</t>
+          <t>8,49; 23,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,67</t>
+          <t>-2,67; 0,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,21</t>
+          <t>-2,4; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 18,11</t>
+          <t>7,41; 17,55</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 242,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,46; 1731,69</t>
+          <t>14,37; 1609,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>288,97; —</t>
+          <t>322,75; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 191,69</t>
+          <t>-90,22; 172,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,91; 190,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>190,74; 2038,79</t>
+          <t>205,5; 2083,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,58</t>
+          <t>-0,84; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,02</t>
+          <t>-0,78; 2,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,66; 23,63</t>
+          <t>9,27; 23,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,15</t>
+          <t>-3,67; 1,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,47; 41,13</t>
+          <t>17,32; 42,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,12</t>
+          <t>-1,05; 1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,24</t>
+          <t>-0,88; 1,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,48; 26,37</t>
+          <t>13,25; 25,64</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>563,61; —</t>
+          <t>579,58; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,25; —</t>
+          <t>-89,66; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,76; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>883,29; 10913,69</t>
+          <t>925,26; 11848,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,22</t>
+          <t>-0,69; 0,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,33</t>
+          <t>-0,27; 1,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,38; 25,09</t>
+          <t>13,67; 25,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,48</t>
+          <t>-2,08; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,11</t>
+          <t>-2,94; 0,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 10,0</t>
+          <t>-1,8; 10,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,49</t>
+          <t>-0,99; 0,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,47</t>
+          <t>-1,03; 0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 15,6</t>
+          <t>2,53; 15,76</t>
         </is>
       </c>
     </row>
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1658,33; —</t>
+          <t>1862,52; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,82; 279,7</t>
+          <t>-79,78; 220,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,43</t>
+          <t>-100,0; 60,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 679,56</t>
+          <t>-60,77; 803,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,75; 138,9</t>
+          <t>-81,25; 114,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 141,31</t>
+          <t>-82,69; 145,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>239,35; 2685,38</t>
+          <t>239,72; 2457,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,98</t>
+          <t>0,22; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,68; 28,64</t>
+          <t>11,31; 27,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,4</t>
+          <t>0,36; 2,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,06</t>
+          <t>0,2; 2,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,24; 22,16</t>
+          <t>14,25; 22,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,87</t>
+          <t>0,38; 1,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,67</t>
+          <t>0,33; 1,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,24</t>
+          <t>14,78; 22,34</t>
         </is>
       </c>
     </row>
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,91; 71,13</t>
+          <t>3,09; 58,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,11</t>
+          <t>-0,27; 0,99</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,33</t>
+          <t>-0,22; 1,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,66</t>
+          <t>17,62; 26,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,87</t>
+          <t>-0,24; 0,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,18</t>
+          <t>-0,24; 1,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17,57; 27,83</t>
+          <t>17,11; 26,91</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2391,24; —</t>
+          <t>2348,34; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2678,24; —</t>
+          <t>2579,11; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,73</t>
+          <t>-0,34; 0,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,96</t>
+          <t>-0,24; 1,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13,34; 19,4</t>
+          <t>12,88; 19,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,97</t>
+          <t>-0,19; 1,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,8</t>
+          <t>-0,32; 0,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,56; 17,22</t>
+          <t>5,03; 17,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,68</t>
+          <t>-0,15; 0,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,67</t>
+          <t>-0,14; 0,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,95</t>
+          <t>7,86; 16,9</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 235,13</t>
+          <t>-41,36; 270,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 291,02</t>
+          <t>-34,86; 304,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1299,12; 5820,65</t>
+          <t>1331,01; 6008,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 185,06</t>
+          <t>-20,68; 193,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 163,0</t>
+          <t>-32,15; 181,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>570,94; 2988,04</t>
+          <t>547,57; 2878,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 136,88</t>
+          <t>-16,32; 133,81</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 125,96</t>
+          <t>-17,04; 140,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1085,66; 3255,7</t>
+          <t>1045,61; 3206,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,69</t>
+          <t>11,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>9,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,43</t>
+          <t>10,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,64</t>
+          <t>0,54; 5,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,76</t>
+          <t>-0,42; 3,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 21,84</t>
+          <t>5,54; 19,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,36</t>
+          <t>-1,22; 5,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 4,33</t>
+          <t>-1,7; 4,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 19,23</t>
+          <t>4,16; 18,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,8</t>
+          <t>0,27; 4,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,13</t>
+          <t>-0,39; 3,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 17,99</t>
+          <t>6,36; 15,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2072,17%</t>
+          <t>1845,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>498,82%</t>
+          <t>480,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>948,8%</t>
+          <t>878,63%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,89; —</t>
+          <t>-26,04; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>348,54; —</t>
+          <t>253,96; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 692,4</t>
+          <t>-54,71; 1090,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 609,32</t>
+          <t>-58,64; 686,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>106,62; 2411,43</t>
+          <t>62,11; 2285,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 913,9</t>
+          <t>0,22; 771,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 519,26</t>
+          <t>-31,78; 502,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>345,61; 3188,12</t>
+          <t>298,4; 2387,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>14,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,1</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 0,71</t>
+          <t>-6,16; 0,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 1,27</t>
+          <t>-5,47; 1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 17,84</t>
+          <t>1,2; 16,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,27</t>
+          <t>-1,59; 2,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,08</t>
+          <t>-1,43; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 23,06</t>
+          <t>8,87; 21,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,87</t>
+          <t>-2,83; 0,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,32</t>
+          <t>-2,39; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 17,55</t>
+          <t>7,29; 16,93</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>342,91%</t>
+          <t>296,29%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1505,36%</t>
+          <t>1493,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>679,38%</t>
+          <t>643,74%</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 211,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 1609,37</t>
+          <t>-11,36; 1581,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>322,75; —</t>
+          <t>302,3; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 172,19</t>
+          <t>-91,75; 159,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,91; 190,23</t>
+          <t>-79,5; 187,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>205,5; 2083,9</t>
+          <t>183,56; 1982,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>13,97</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,15</t>
+          <t>29,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,81</t>
+          <t>18,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,67</t>
+          <t>-0,89; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,28</t>
+          <t>-0,54; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 23,28</t>
+          <t>8,66; 21,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,14</t>
+          <t>-3,63; 1,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-5,44; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 42,84</t>
+          <t>17,48; 42,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,13</t>
+          <t>-0,91; 1,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,27</t>
+          <t>-0,86; 1,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,25; 25,64</t>
+          <t>13,04; 25,81</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2690,75%</t>
+          <t>2472,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3084,19%</t>
+          <t>3206,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2854,6%</t>
+          <t>2751,56%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>579,58; —</t>
+          <t>577,76; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,66; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>925,26; 11848,09</t>
+          <t>892,25; 11457,41</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,5</t>
+          <t>17,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>13,72</t>
         </is>
       </c>
     </row>
@@ -1330,42 +1330,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,33</t>
+          <t>-0,29; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,67; 25,24</t>
+          <t>12,28; 23,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,27</t>
+          <t>-2,34; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,13</t>
+          <t>-3,06; 0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 10,22</t>
+          <t>5,42; 13,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,45</t>
+          <t>-0,9; 0,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,5</t>
+          <t>-1,0; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 15,76</t>
+          <t>10,46; 17,85</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6846,65%</t>
+          <t>6310,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>148,68%</t>
+          <t>533,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1041,41%</t>
+          <t>1698,06%</t>
         </is>
       </c>
     </row>
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1862,52; —</t>
+          <t>1648,44; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 220,39</t>
+          <t>-82,5; 215,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,34</t>
+          <t>-100,0; 79,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 803,85</t>
+          <t>154,93; 1570,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 114,59</t>
+          <t>-80,51; 126,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 145,36</t>
+          <t>-82,57; 130,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>239,72; 2457,92</t>
+          <t>778,42; 4035,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,48</t>
+          <t>16,61</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,0</t>
+          <t>16,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,14</t>
+          <t>16,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,15</t>
+          <t>0,21; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,31; 27,57</t>
+          <t>10,2; 25,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,26</t>
+          <t>0,35; 2,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,1</t>
+          <t>0,21; 2,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,25; 22,35</t>
+          <t>12,98; 20,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,72</t>
+          <t>0,36; 1,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,61</t>
+          <t>0,33; 1,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,78; 22,34</t>
+          <t>13,22; 20,17</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20,94</t>
+          <t>16,2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,73</t>
+          <t>20,38</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21,67</t>
+          <t>19,97</t>
         </is>
       </c>
     </row>
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,09; 58,76</t>
+          <t>2,52; 52,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,99</t>
+          <t>-0,25; 1,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,22</t>
+          <t>-0,13; 1,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,62; 26,89</t>
+          <t>16,46; 24,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,88</t>
+          <t>-0,23; 0,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,11</t>
+          <t>-0,22; 1,06</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17,11; 26,91</t>
+          <t>16,31; 25,19</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8275,76%</t>
+          <t>7761,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9267,89%</t>
+          <t>8540,2%</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2348,34; —</t>
+          <t>2284,73; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2579,11; —</t>
+          <t>2201,54; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16,14</t>
+          <t>14,61</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,57</t>
+          <t>15,77</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>15,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,83</t>
+          <t>-0,3; 0,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,0</t>
+          <t>-0,2; 0,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,57</t>
+          <t>11,7; 17,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,0</t>
+          <t>-0,18; 1,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,82</t>
+          <t>-0,42; 0,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,03; 17,07</t>
+          <t>13,8; 17,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,68</t>
+          <t>-0,11; 0,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,13; 0,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,86; 16,9</t>
+          <t>13,69; 17,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2785,81%</t>
+          <t>2521,08%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1631,77%</t>
+          <t>2047,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2022,69%</t>
+          <t>2237,4%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 270,29</t>
+          <t>-42,96; 234,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 304,18</t>
+          <t>-33,2; 277,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1331,01; 6008,04</t>
+          <t>1258,2; 5539,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 193,97</t>
+          <t>-21,01; 214,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 181,51</t>
+          <t>-41,63; 153,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>547,57; 2878,54</t>
+          <t>1178,05; 3727,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 133,81</t>
+          <t>-15,26; 144,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 140,62</t>
+          <t>-19,31; 142,49</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1045,61; 3206,69</t>
+          <t>1431,57; 3480,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
